--- a/public/StructureDefinition-pghd-sleep.xlsx
+++ b/public/StructureDefinition-pghd-sleep.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-sleep.xlsx
+++ b/public/StructureDefinition-pghd-sleep.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3679" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3679" uniqueCount="580">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -981,6 +981,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/CodeSystem/observation-pghd-codes</t>
   </si>
   <si>
     <t>Observation.code.coding:PGHDCode.version</t>
@@ -6291,7 +6294,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>92</v>
@@ -6325,7 +6328,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6402,10 +6405,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6522,10 +6525,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6642,10 +6645,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6762,10 +6765,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6884,13 +6887,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>301</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>82</v>
@@ -7008,7 +7011,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>307</v>
@@ -7126,7 +7129,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>309</v>
@@ -7246,7 +7249,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>311</v>
@@ -7291,7 +7294,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7368,10 +7371,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7488,10 +7491,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7608,10 +7611,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7728,10 +7731,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7850,10 +7853,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7972,10 +7975,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7998,19 +8001,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8059,7 +8062,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8074,19 +8077,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8094,10 +8097,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8120,16 +8123,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8179,7 +8182,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8203,10 +8206,10 @@
         <v>295</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8214,14 +8217,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8240,19 +8243,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8301,7 +8304,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8316,19 +8319,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8336,14 +8339,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8362,19 +8365,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8423,7 +8426,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8438,19 +8441,19 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8458,10 +8461,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8484,16 +8487,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8543,7 +8546,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8564,13 +8567,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8578,10 +8581,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8604,17 +8607,17 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8663,7 +8666,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8678,19 +8681,19 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8698,10 +8701,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8727,16 +8730,16 @@
         <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8785,7 +8788,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8794,7 +8797,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -8803,27 +8806,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8938,10 +8941,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9058,10 +9061,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9178,13 +9181,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="B59" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="C59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>82</v>
@@ -9247,7 +9250,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9300,10 +9303,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9418,10 +9421,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9538,10 +9541,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9586,7 +9589,7 @@
         <v>82</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>82</v>
@@ -9660,10 +9663,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9780,10 +9783,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9900,10 +9903,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10020,10 +10023,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10142,10 +10145,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10264,10 +10267,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10293,16 +10296,16 @@
         <v>190</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10327,13 +10330,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10351,7 +10354,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10360,7 +10363,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10375,7 +10378,7 @@
         <v>135</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10386,14 +10389,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10415,16 +10418,16 @@
         <v>190</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10449,13 +10452,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10473,7 +10476,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10491,27 +10494,27 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10534,19 +10537,19 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10595,7 +10598,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10616,10 +10619,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10630,10 +10633,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10659,13 +10662,13 @@
         <v>190</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10694,10 +10697,10 @@
         <v>290</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10715,7 +10718,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10733,27 +10736,27 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10779,16 +10782,16 @@
         <v>190</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10816,10 +10819,10 @@
         <v>290</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10837,7 +10840,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10858,10 +10861,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10872,10 +10875,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10898,16 +10901,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10957,7 +10960,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10975,27 +10978,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11018,16 +11021,16 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11077,7 +11080,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11095,27 +11098,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11138,19 +11141,19 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11199,7 +11202,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11211,7 +11214,7 @@
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11220,10 +11223,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11234,10 +11237,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11352,10 +11355,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11472,14 +11475,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11501,10 +11504,10 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>141</v>
@@ -11559,7 +11562,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11594,10 +11597,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11620,13 +11623,13 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11677,7 +11680,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11686,7 +11689,7 @@
         <v>92</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
@@ -11698,10 +11701,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11712,10 +11715,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11738,13 +11741,13 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11795,7 +11798,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11804,7 +11807,7 @@
         <v>92</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>104</v>
@@ -11816,10 +11819,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11830,10 +11833,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11859,16 +11862,16 @@
         <v>190</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11896,10 +11899,10 @@
         <v>116</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -11917,7 +11920,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11935,13 +11938,13 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -11952,10 +11955,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11981,16 +11984,16 @@
         <v>190</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12018,10 +12021,10 @@
         <v>290</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12039,7 +12042,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12057,13 +12060,13 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12074,10 +12077,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12100,17 +12103,17 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12159,7 +12162,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12183,7 +12186,7 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12194,10 +12197,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12223,10 +12226,10 @@
         <v>205</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12277,7 +12280,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12298,10 +12301,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12312,10 +12315,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12338,16 +12341,16 @@
         <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12397,7 +12400,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12418,10 +12421,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12432,10 +12435,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12458,16 +12461,16 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12517,7 +12520,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12538,10 +12541,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12552,10 +12555,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12578,19 +12581,19 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12639,7 +12642,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12660,10 +12663,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12674,10 +12677,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12792,10 +12795,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12912,14 +12915,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12941,10 +12944,10 @@
         <v>138</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>141</v>
@@ -12999,7 +13002,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13034,10 +13037,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13063,13 +13066,13 @@
         <v>190</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>289</v>
@@ -13121,7 +13124,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>92</v>
@@ -13139,7 +13142,7 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>295</v>
@@ -13156,10 +13159,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13182,19 +13185,19 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13243,7 +13246,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13261,27 +13264,27 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13307,16 +13310,16 @@
         <v>190</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13341,13 +13344,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13365,7 +13368,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13374,7 +13377,7 @@
         <v>92</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>104</v>
@@ -13389,7 +13392,7 @@
         <v>135</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13400,14 +13403,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13429,16 +13432,16 @@
         <v>190</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13463,13 +13466,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13487,7 +13490,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13505,27 +13508,27 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13551,16 +13554,16 @@
         <v>83</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13609,7 +13612,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13630,10 +13633,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
